--- a/membership_forms/008_nobility_membership_application_form--membership_forms.xlsx
+++ b/membership_forms/008_nobility_membership_application_form--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_none}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': None}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_1}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 1}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_0}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': 0}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_none}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': None}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -854,78 +854,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_none}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': None}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noble_society_member_of_choices</t>
+          <t>nobility_application_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_none}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': None}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noble_society_member_of_choices</t>
+          <t>nobility_application_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_none}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': 'None', 'value': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>nobility_application_status_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>nobility_application_status_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
